--- a/datasets/rbf_treinamentos.xlsx
+++ b/datasets/rbf_treinamentos.xlsx
@@ -491,7 +491,7 @@
         <v>0.61211667</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02980551</v>
+        <v>0.05961102</v>
       </c>
       <c r="E2" t="n">
         <v>0.39896923</v>
@@ -500,22 +500,22 @@
         <v>0.15713077</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03845986</v>
+        <v>0.07691973000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>2.37763694</v>
+        <v>1.59789596</v>
       </c>
       <c r="I2" t="n">
-        <v>2.69753867</v>
+        <v>2.50396189</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.00255418</v>
+        <v>-1.29546691</v>
       </c>
       <c r="K2" t="n">
-        <v>348</v>
+        <v>239</v>
       </c>
       <c r="L2" t="n">
-        <v>0.23707859</v>
+        <v>0.12244239</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>0.61211667</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02980551</v>
+        <v>0.05961102</v>
       </c>
       <c r="E3" t="n">
         <v>0.39896923</v>
@@ -540,22 +540,22 @@
         <v>0.15713077</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03845986</v>
+        <v>0.07691973000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>2.37754614</v>
+        <v>1.59802465</v>
       </c>
       <c r="I3" t="n">
-        <v>2.69750073</v>
+        <v>2.50403071</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.00253198</v>
+        <v>-1.29552548</v>
       </c>
       <c r="K3" t="n">
-        <v>346</v>
+        <v>238</v>
       </c>
       <c r="L3" t="n">
-        <v>0.23707866</v>
+        <v>0.12244233</v>
       </c>
     </row>
     <row r="4">
@@ -565,37 +565,37 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0.16483333</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.61211667</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.05961102</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.39896923</v>
       </c>
-      <c r="C4" t="n">
+      <c r="F4" t="n">
         <v>0.15713077</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.03845986</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.16483333</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.61211667</v>
-      </c>
       <c r="G4" t="n">
-        <v>0.02980551</v>
+        <v>0.07691973000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>2.69752924</v>
+        <v>1.59797999</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3776144</v>
+        <v>2.50400582</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.00254867</v>
+        <v>-1.29550477</v>
       </c>
       <c r="K4" t="n">
-        <v>348</v>
+        <v>239</v>
       </c>
       <c r="L4" t="n">
-        <v>0.23707861</v>
+        <v>0.12244236</v>
       </c>
     </row>
     <row r="5">
@@ -611,7 +611,7 @@
         <v>0.61211667</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02980551</v>
+        <v>0.05961102</v>
       </c>
       <c r="E5" t="n">
         <v>0.39896923</v>
@@ -620,22 +620,22 @@
         <v>0.15713077</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03845986</v>
+        <v>0.07691973000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>2.37755554</v>
+        <v>1.59803896</v>
       </c>
       <c r="I5" t="n">
-        <v>2.69750468</v>
+        <v>2.50403867</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.00253428</v>
+        <v>-1.29553211</v>
       </c>
       <c r="K5" t="n">
-        <v>346</v>
+        <v>240</v>
       </c>
       <c r="L5" t="n">
-        <v>0.23707865</v>
+        <v>0.12244233</v>
       </c>
     </row>
     <row r="6">
@@ -645,37 +645,37 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>0.16483333</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.61211667</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.05961102</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.39896923</v>
       </c>
-      <c r="C6" t="n">
+      <c r="F6" t="n">
         <v>0.15713077</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.03845986</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.16483333</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.61211667</v>
-      </c>
       <c r="G6" t="n">
-        <v>0.02980551</v>
+        <v>0.07691973000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>2.69754863</v>
+        <v>1.59787789</v>
       </c>
       <c r="I6" t="n">
-        <v>2.37766096</v>
+        <v>2.5039535</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.00256003</v>
+        <v>-1.29545916</v>
       </c>
       <c r="K6" t="n">
-        <v>347</v>
+        <v>239</v>
       </c>
       <c r="L6" t="n">
-        <v>0.23707857</v>
+        <v>0.1224424</v>
       </c>
     </row>
   </sheetData>
